--- a/data/input-data/oyanthabal/Índices de Precios.xlsx
+++ b/data/input-data/oyanthabal/Índices de Precios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emi\Desktop\Uruguay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF4CCD4-104C-4A2B-B1AF-FDADFE3AA698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0F7CDF-DAEC-449A-A409-5BA024CDE336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FA2A47A2-88B7-4D5A-99BC-F6AA3835C400}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>GDP Price index (base 2005)</t>
   </si>
@@ -64,7 +64,13 @@
     <t>Cuentas Nacionales Uruguay</t>
   </si>
   <si>
-    <t>2005 = 1</t>
+    <t>Índice de precios implícitos base 2016</t>
+  </si>
+  <si>
+    <t>BCU</t>
+  </si>
+  <si>
+    <t>Oyanthabal + BCU</t>
   </si>
 </sst>
 </file>
@@ -502,7 +508,7 @@
     <col min="1" max="1" width="12.140625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="4" max="5" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
@@ -515,8 +521,8 @@
       <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>6</v>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>6</v>
@@ -535,7 +541,7 @@
       <c r="E2" s="4">
         <v>4</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>5</v>
       </c>
     </row>
@@ -550,13 +556,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
@@ -564,11 +570,9 @@
         <v>10</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>10</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E4" s="10"/>
       <c r="F4" s="10" t="s">
         <v>10</v>
       </c>
@@ -586,12 +590,9 @@
       <c r="D5" s="6">
         <v>2.48726119359941E-8</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="6"/>
+      <c r="F5" s="13">
         <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F5" s="8">
-        <f t="shared" ref="F5:F54" si="0">E5/E$55</f>
-        <v>1.9010503303074951E-8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -607,12 +608,9 @@
       <c r="D6" s="6">
         <v>2.7428836633122E-8</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="6"/>
+      <c r="F6" s="13">
         <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F6" s="8">
-        <f t="shared" si="0"/>
-        <v>1.9010503303074951E-8</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -628,12 +626,9 @@
       <c r="D7" s="6">
         <v>3.2185817495745301E-8</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="6"/>
+      <c r="F7" s="13">
         <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="F7" s="8">
-        <f t="shared" si="0"/>
-        <v>2.3763129128843688E-8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -649,12 +644,9 @@
       <c r="D8" s="6">
         <v>3.6089394171667598E-8</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="6"/>
+      <c r="F8" s="13">
         <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="F8" s="8">
-        <f t="shared" si="0"/>
-        <v>2.8515754954612421E-8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -670,12 +662,9 @@
       <c r="D9" s="6">
         <v>4.9744761759474E-8</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="6"/>
+      <c r="F9" s="13">
         <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="0"/>
-        <v>3.8021006606149901E-8</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -691,12 +680,9 @@
       <c r="D10" s="6">
         <v>7.3608280505886897E-8</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="6"/>
+      <c r="F10" s="13">
         <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="F10" s="8">
-        <f t="shared" si="0"/>
-        <v>5.2278884083456115E-8</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -712,12 +698,9 @@
       <c r="D11" s="6">
         <v>9.1028826193151495E-8</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="6"/>
+      <c r="F11" s="13">
         <v>1.4E-3</v>
-      </c>
-      <c r="F11" s="8">
-        <f t="shared" si="0"/>
-        <v>6.6536761560762323E-8</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -733,12 +716,9 @@
       <c r="D12" s="6">
         <v>1.01547218252891E-7</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="6"/>
+      <c r="F12" s="13">
         <v>1.5E-3</v>
-      </c>
-      <c r="F12" s="8">
-        <f t="shared" si="0"/>
-        <v>7.1289387386531056E-8</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -754,12 +734,9 @@
       <c r="D13" s="6">
         <v>1.19957510610822E-7</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="6"/>
+      <c r="F13" s="13">
         <v>1.8E-3</v>
-      </c>
-      <c r="F13" s="8">
-        <f t="shared" si="0"/>
-        <v>8.554726486383727E-8</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -775,12 +752,9 @@
       <c r="D14" s="6">
         <v>1.7132997303875101E-7</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="6"/>
+      <c r="F14" s="13">
         <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="F14" s="8">
-        <f t="shared" si="0"/>
-        <v>1.2356827146998715E-7</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -796,12 +770,9 @@
       <c r="D15" s="6">
         <v>2.7293622643362701E-7</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="6"/>
+      <c r="F15" s="13">
         <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="F15" s="8">
-        <f t="shared" si="0"/>
-        <v>1.9485765885651825E-7</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -817,12 +788,9 @@
       <c r="D16" s="6">
         <v>5.0080907919269697E-7</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="6"/>
+      <c r="F16" s="13">
         <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="F16" s="8">
-        <f t="shared" si="0"/>
-        <v>3.3743643362958039E-7</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -838,12 +806,9 @@
       <c r="D17" s="6">
         <v>8.9030436748660395E-7</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="6"/>
+      <c r="F17" s="13">
         <v>1.35E-2</v>
-      </c>
-      <c r="F17" s="8">
-        <f t="shared" si="0"/>
-        <v>6.4160448647877955E-7</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -859,12 +824,9 @@
       <c r="D18" s="6">
         <v>1.9332653579659701E-6</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="6"/>
+      <c r="F18" s="13">
         <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="0"/>
-        <v>1.4495508768594648E-6</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -880,12 +842,9 @@
       <c r="D19" s="6">
         <v>2.46189953113534E-6</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="6"/>
+      <c r="F19" s="13">
         <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="0"/>
-        <v>1.7584715555344327E-6</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -901,12 +860,9 @@
       <c r="D20" s="6">
         <v>2.8687316275072501E-6</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="6"/>
+      <c r="F20" s="13">
         <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" si="0"/>
-        <v>2.0436291050805569E-6</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -922,12 +878,9 @@
       <c r="D21" s="6">
         <v>3.4421697411730599E-6</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="6"/>
+      <c r="F21" s="13">
         <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="0"/>
-        <v>2.5188916876574307E-6</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -943,12 +896,9 @@
       <c r="D22" s="6">
         <v>6.0146935106344003E-6</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="6"/>
+      <c r="F22" s="13">
         <v>9.4E-2</v>
-      </c>
-      <c r="F22" s="8">
-        <f t="shared" si="0"/>
-        <v>4.4674682762226127E-6</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -964,12 +914,9 @@
       <c r="D23" s="7">
         <v>1.23571865053856E-5</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="7"/>
+      <c r="F23" s="13">
         <v>0.185</v>
-      </c>
-      <c r="F23" s="8">
-        <f t="shared" si="0"/>
-        <v>8.7923577776721633E-6</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -985,12 +932,9 @@
       <c r="D24" s="7">
         <v>2.1266638012811802E-5</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="7"/>
+      <c r="F24" s="13">
         <v>0.32700000000000001</v>
-      </c>
-      <c r="F24" s="8">
-        <f t="shared" si="0"/>
-        <v>1.5541086450263773E-5</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1006,12 +950,9 @@
       <c r="D25" s="7">
         <v>3.6085441634308399E-5</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="7"/>
+      <c r="F25" s="13">
         <v>0.59</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="0"/>
-        <v>2.8040492372035548E-5</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1027,12 +968,9 @@
       <c r="D26" s="7">
         <v>5.3706946472405702E-5</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="7"/>
+      <c r="F26" s="13">
         <v>0.89</v>
-      </c>
-      <c r="F26" s="8">
-        <f t="shared" si="0"/>
-        <v>4.2298369849341759E-5</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1048,12 +986,9 @@
       <c r="D27" s="7">
         <v>8.3649428916301495E-5</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="7"/>
+      <c r="F27" s="13">
         <v>1.41</v>
-      </c>
-      <c r="F27" s="8">
-        <f t="shared" si="0"/>
-        <v>6.7012024143339185E-5</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1069,12 +1004,9 @@
       <c r="D28" s="7">
         <v>1.2342228567796201E-4</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="7"/>
+      <c r="F28" s="13">
         <v>2.04</v>
-      </c>
-      <c r="F28" s="8">
-        <f t="shared" si="0"/>
-        <v>9.6953566845682241E-5</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1090,12 +1022,9 @@
       <c r="D29" s="7">
         <v>2.1658472538499699E-4</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="7"/>
+      <c r="F29" s="13">
         <v>3.41</v>
-      </c>
-      <c r="F29" s="8">
-        <f t="shared" si="0"/>
-        <v>1.6206454065871394E-4</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1111,12 +1040,9 @@
       <c r="D30" s="7">
         <v>3.26937153201872E-4</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="7"/>
+      <c r="F30" s="13">
         <v>5.58</v>
-      </c>
-      <c r="F30" s="8">
-        <f t="shared" si="0"/>
-        <v>2.6519652107789555E-4</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1132,12 +1058,9 @@
       <c r="D31" s="7">
         <v>4.2610248803528198E-4</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="7"/>
+      <c r="F31" s="13">
         <v>7.47</v>
-      </c>
-      <c r="F31" s="8">
-        <f t="shared" si="0"/>
-        <v>3.5502114918492468E-4</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1153,12 +1076,9 @@
       <c r="D32" s="7">
         <v>4.9424215811845603E-4</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="7"/>
+      <c r="F32" s="13">
         <v>9</v>
-      </c>
-      <c r="F32" s="8">
-        <f t="shared" si="0"/>
-        <v>4.2773632431918637E-4</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1174,12 +1094,9 @@
       <c r="D33" s="7">
         <v>7.5466382602825603E-4</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="7"/>
+      <c r="F33" s="13">
         <v>13</v>
-      </c>
-      <c r="F33" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1784135734993582E-4</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1195,12 +1112,9 @@
       <c r="D34" s="7">
         <v>1.1788563953482E-3</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="7"/>
+      <c r="F34" s="13">
         <v>21</v>
-      </c>
-      <c r="F34" s="8">
-        <f t="shared" si="0"/>
-        <v>9.9805142341143484E-4</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1216,12 +1130,9 @@
       <c r="D35" s="7">
         <v>2.0516357873350201E-3</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="7"/>
+      <c r="F35" s="13">
         <v>35</v>
-      </c>
-      <c r="F35" s="8">
-        <f t="shared" si="0"/>
-        <v>1.6634190390190581E-3</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1237,12 +1148,9 @@
       <c r="D36" s="7">
         <v>3.5062725461022801E-3</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="7"/>
+      <c r="F36" s="13">
         <v>63</v>
-      </c>
-      <c r="F36" s="8">
-        <f t="shared" si="0"/>
-        <v>2.9941542702343043E-3</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1258,12 +1166,9 @@
       <c r="D37" s="7">
         <v>6.0614362977402299E-3</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="7"/>
+      <c r="F37" s="13">
         <v>102</v>
-      </c>
-      <c r="F37" s="8">
-        <f t="shared" si="0"/>
-        <v>4.8476783422841119E-3</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1279,12 +1184,9 @@
       <c r="D38" s="7">
         <v>1.05873087274641E-2</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="7"/>
+      <c r="F38" s="13">
         <v>166</v>
-      </c>
-      <c r="F38" s="8">
-        <f t="shared" si="0"/>
-        <v>7.8893588707761031E-3</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1300,12 +1202,9 @@
       <c r="D39" s="8">
         <v>1.8642076681235398E-2</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="8"/>
+      <c r="F39" s="13">
         <v>300</v>
-      </c>
-      <c r="F39" s="8">
-        <f t="shared" si="0"/>
-        <v>1.4257877477306212E-2</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1321,12 +1220,9 @@
       <c r="D40" s="8">
         <v>3.8558651841471801E-2</v>
       </c>
-      <c r="E40" s="13">
+      <c r="E40" s="8"/>
+      <c r="F40" s="13">
         <v>637</v>
-      </c>
-      <c r="F40" s="8">
-        <f t="shared" si="0"/>
-        <v>3.0274226510146857E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1342,12 +1238,9 @@
       <c r="D41" s="8">
         <v>7.7428922230050906E-2</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="8"/>
+      <c r="F41" s="14">
         <v>1286</v>
-      </c>
-      <c r="F41" s="8">
-        <f t="shared" si="0"/>
-        <v>6.1118768119385963E-2</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1363,12 +1256,9 @@
       <c r="D42" s="8">
         <v>0.123594850688727</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="8"/>
+      <c r="F42" s="14">
         <v>2167</v>
-      </c>
-      <c r="F42" s="8">
-        <f t="shared" si="0"/>
-        <v>0.10298940164440853</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1384,12 +1274,9 @@
       <c r="D43" s="8">
         <v>0.18273737074882901</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="8"/>
+      <c r="F43" s="14">
         <v>3339</v>
-      </c>
-      <c r="F43" s="8">
-        <f t="shared" si="0"/>
-        <v>0.15869017632241814</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1405,12 +1292,9 @@
       <c r="D44" s="8">
         <v>0.25392670148130397</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="8"/>
+      <c r="F44" s="14">
         <v>4832</v>
-      </c>
-      <c r="F44" s="8">
-        <f t="shared" si="0"/>
-        <v>0.22964687990114538</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1426,12 +1310,9 @@
       <c r="D45" s="8">
         <v>0.35815936395734299</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="8"/>
+      <c r="F45" s="14">
         <v>6874</v>
-      </c>
-      <c r="F45" s="8">
-        <f t="shared" si="0"/>
-        <v>0.32669549926334301</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1447,12 +1328,9 @@
       <c r="D46" s="8">
         <v>0.45282710784393498</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="8"/>
+      <c r="F46" s="14">
         <v>8822</v>
-      </c>
-      <c r="F46" s="8">
-        <f t="shared" si="0"/>
-        <v>0.41927665034931799</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1468,12 +1346,9 @@
       <c r="D47" s="8">
         <v>0.54013527554621599</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="8"/>
+      <c r="F47" s="14">
         <v>10571</v>
-      </c>
-      <c r="F47" s="8">
-        <f t="shared" si="0"/>
-        <v>0.5024000760420132</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1489,12 +1364,9 @@
       <c r="D48" s="8">
         <v>0.60702511758938404</v>
       </c>
-      <c r="E48" s="14">
+      <c r="E48" s="8"/>
+      <c r="F48" s="14">
         <v>11713</v>
-      </c>
-      <c r="F48" s="8">
-        <f t="shared" si="0"/>
-        <v>0.55667506297229219</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1510,12 +1382,9 @@
       <c r="D49" s="8">
         <v>0.63328560802950296</v>
       </c>
-      <c r="E49" s="14">
+      <c r="E49" s="8"/>
+      <c r="F49" s="14">
         <v>12376</v>
-      </c>
-      <c r="F49" s="8">
-        <f t="shared" si="0"/>
-        <v>0.58818497219713894</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1531,12 +1400,9 @@
       <c r="D50" s="8">
         <v>0.65569953943060999</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="8"/>
+      <c r="F50" s="14">
         <v>12966</v>
-      </c>
-      <c r="F50" s="8">
-        <f t="shared" si="0"/>
-        <v>0.61622546456917449</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1552,12 +1418,9 @@
       <c r="D51" s="8">
         <v>0.68734765358136096</v>
       </c>
-      <c r="E51" s="14">
+      <c r="E51" s="8"/>
+      <c r="F51" s="14">
         <v>13532</v>
-      </c>
-      <c r="F51" s="8">
-        <f t="shared" si="0"/>
-        <v>0.64312532674302547</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1573,12 +1436,9 @@
       <c r="D52" s="8">
         <v>0.77406533491190999</v>
       </c>
-      <c r="E52" s="14">
+      <c r="E52" s="8"/>
+      <c r="F52" s="14">
         <v>15422</v>
-      </c>
-      <c r="F52" s="8">
-        <f t="shared" si="0"/>
-        <v>0.73294995485005465</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1594,12 +1454,9 @@
       <c r="D53" s="8">
         <v>0.90210839846924895</v>
       </c>
-      <c r="E53" s="14">
+      <c r="E53" s="8"/>
+      <c r="F53" s="14">
         <v>18410</v>
-      </c>
-      <c r="F53" s="8">
-        <f t="shared" si="0"/>
-        <v>0.87495841452402456</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1615,12 +1472,9 @@
       <c r="D54" s="8">
         <v>0.99326695734614601</v>
       </c>
-      <c r="E54" s="14">
+      <c r="E54" s="8"/>
+      <c r="F54" s="14">
         <v>20096</v>
-      </c>
-      <c r="F54" s="8">
-        <f t="shared" si="0"/>
-        <v>0.95508768594648541</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1636,12 +1490,9 @@
       <c r="D55" s="8">
         <v>1</v>
       </c>
-      <c r="E55" s="14">
+      <c r="E55" s="8"/>
+      <c r="F55" s="14">
         <v>21041</v>
-      </c>
-      <c r="F55" s="8">
-        <f>E55/E$55</f>
-        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1657,12 +1508,9 @@
       <c r="D56" s="8">
         <v>1.0653333463425101</v>
       </c>
-      <c r="E56" s="14">
+      <c r="E56" s="8"/>
+      <c r="F56" s="14">
         <v>22387</v>
-      </c>
-      <c r="F56" s="8">
-        <f t="shared" ref="F56:F74" si="1">E56/E$55</f>
-        <v>1.0639703436148471</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1678,12 +1526,9 @@
       <c r="D57" s="8">
         <v>1.1656608316719199</v>
       </c>
-      <c r="E57" s="14">
+      <c r="E57" s="8"/>
+      <c r="F57" s="14">
         <v>24204</v>
-      </c>
-      <c r="F57" s="8">
-        <f t="shared" si="1"/>
-        <v>1.1503255548690652</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1699,12 +1544,9 @@
       <c r="D58" s="8">
         <v>1.25918805295632</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E58" s="8"/>
+      <c r="F58" s="14">
         <v>26110</v>
-      </c>
-      <c r="F58" s="8">
-        <f t="shared" si="1"/>
-        <v>1.2409106031082173</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1720,12 +1562,9 @@
       <c r="D59" s="8">
         <v>1.35674417719499</v>
       </c>
-      <c r="E59" s="14">
+      <c r="E59" s="8"/>
+      <c r="F59" s="14">
         <v>27954</v>
-      </c>
-      <c r="F59" s="8">
-        <f t="shared" si="1"/>
-        <v>1.3285490233353927</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1741,12 +1580,9 @@
       <c r="D60" s="8">
         <v>1.4233199568561401</v>
       </c>
-      <c r="E60" s="14">
+      <c r="E60" s="8"/>
+      <c r="F60" s="14">
         <v>29826</v>
-      </c>
-      <c r="F60" s="8">
-        <f t="shared" si="1"/>
-        <v>1.4175181787937836</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1762,12 +1598,9 @@
       <c r="D61" s="8">
         <v>1.5515564668378901</v>
       </c>
-      <c r="E61" s="14">
+      <c r="E61" s="8"/>
+      <c r="F61" s="14">
         <v>32240</v>
-      </c>
-      <c r="F61" s="8">
-        <f t="shared" si="1"/>
-        <v>1.5322465662278408</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1783,12 +1616,9 @@
       <c r="D62" s="8">
         <v>1.68433171334606</v>
       </c>
-      <c r="E62" s="14">
+      <c r="E62" s="8"/>
+      <c r="F62" s="14">
         <v>34851</v>
-      </c>
-      <c r="F62" s="8">
-        <f t="shared" si="1"/>
-        <v>1.6563376265386627</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1804,12 +1634,9 @@
       <c r="D63" s="8">
         <v>1.82166757075506</v>
       </c>
-      <c r="E63" s="14">
+      <c r="E63" s="8"/>
+      <c r="F63" s="14">
         <v>37840</v>
-      </c>
-      <c r="F63" s="8">
-        <f t="shared" si="1"/>
-        <v>1.7983936124708901</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1825,12 +1652,9 @@
       <c r="D64" s="8">
         <v>1.9923987435385999</v>
       </c>
-      <c r="E64" s="14">
+      <c r="E64" s="8"/>
+      <c r="F64" s="14">
         <v>41199</v>
-      </c>
-      <c r="F64" s="8">
-        <f t="shared" si="1"/>
-        <v>1.9580343139584619</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1846,12 +1670,9 @@
       <c r="D65" s="8">
         <v>2.1720390055257699</v>
       </c>
-      <c r="E65" s="14">
+      <c r="E65" s="8"/>
+      <c r="F65" s="14">
         <v>44769</v>
-      </c>
-      <c r="F65" s="8">
-        <f t="shared" si="1"/>
-        <v>2.1277030559384058</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1867,12 +1688,11 @@
       <c r="D66" s="8">
         <v>2.3315859340805098</v>
       </c>
-      <c r="E66" s="14">
+      <c r="E66" s="8">
+        <v>100</v>
+      </c>
+      <c r="F66" s="14">
         <v>49085</v>
-      </c>
-      <c r="F66" s="8">
-        <f t="shared" si="1"/>
-        <v>2.3328263865785845</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1888,12 +1708,11 @@
       <c r="D67" s="8">
         <v>2.4413193635633998</v>
       </c>
-      <c r="E67" s="14">
+      <c r="E67" s="8">
+        <v>105.68017140723612</v>
+      </c>
+      <c r="F67" s="14">
         <v>52138</v>
-      </c>
-      <c r="F67" s="8">
-        <f t="shared" si="1"/>
-        <v>2.4779240530393043</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1909,12 +1728,11 @@
       <c r="D68" s="8">
         <v>2.5769357028766602</v>
       </c>
-      <c r="E68" s="14">
+      <c r="E68" s="8">
+        <v>113.63319617689957</v>
+      </c>
+      <c r="F68" s="14">
         <v>56103</v>
-      </c>
-      <c r="F68" s="8">
-        <f t="shared" si="1"/>
-        <v>2.6663656670310347</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1930,57 +1748,83 @@
       <c r="D69" s="8">
         <v>2.7745329798963199</v>
       </c>
-      <c r="E69" s="14">
+      <c r="E69" s="8">
+        <v>123.01513246121117</v>
+      </c>
+      <c r="F69" s="14">
         <v>60525</v>
       </c>
-      <c r="F69" s="8">
-        <f t="shared" si="1"/>
-        <v>2.876526781046528</v>
-      </c>
     </row>
     <row r="70" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="E70" s="14">
+      <c r="A70" s="2">
+        <v>2020</v>
+      </c>
+      <c r="D70" s="8">
+        <f>(E70/E69-1)*D69+D69</f>
+        <v>3.0720570809110632</v>
+      </c>
+      <c r="E70" s="8">
+        <v>136.20652970245033</v>
+      </c>
+      <c r="F70" s="14">
         <v>66220</v>
       </c>
-      <c r="F70" s="8">
-        <f t="shared" si="1"/>
-        <v>3.147188821824058</v>
-      </c>
     </row>
     <row r="71" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="E71" s="14">
+      <c r="A71" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D71" s="8">
+        <f t="shared" ref="D71:D74" si="0">(E71/E70-1)*D70+D70</f>
+        <v>3.412256929353072</v>
+      </c>
+      <c r="E71" s="8">
+        <v>151.29005176638395</v>
+      </c>
+      <c r="F71" s="14">
         <v>71491</v>
       </c>
-      <c r="F71" s="8">
-        <f t="shared" si="1"/>
-        <v>3.3976997291003279</v>
-      </c>
     </row>
     <row r="72" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="E72" s="14">
+      <c r="A72" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D72" s="8">
+        <f t="shared" si="0"/>
+        <v>3.6166176585179879</v>
+      </c>
+      <c r="E72" s="8">
+        <v>160.35084230311466</v>
+      </c>
+      <c r="F72" s="14">
         <v>77854</v>
       </c>
-      <c r="F72" s="8">
-        <f t="shared" si="1"/>
-        <v>3.7001093103939926</v>
-      </c>
     </row>
     <row r="73" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="E73" s="14">
+      <c r="A73" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D73" s="8">
+        <f t="shared" si="0"/>
+        <v>3.7632011320453107</v>
+      </c>
+      <c r="E73" s="8">
+        <v>166.84994883500454</v>
+      </c>
+      <c r="F73" s="14">
         <v>81824</v>
       </c>
-      <c r="F73" s="8">
-        <f t="shared" si="1"/>
-        <v>3.8887885556770114</v>
-      </c>
     </row>
     <row r="74" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="E74" s="14">
+      <c r="D74" s="8">
+        <f t="shared" si="0"/>
+        <v>3.9207675323421141</v>
+      </c>
+      <c r="E74" s="8">
+        <v>173.83600801843937</v>
+      </c>
+      <c r="F74" s="14">
         <v>86317</v>
-      </c>
-      <c r="F74" s="8">
-        <f t="shared" si="1"/>
-        <v>4.1023240340288005</v>
       </c>
     </row>
   </sheetData>
